--- a/outputs/48365.xlsx
+++ b/outputs/48365.xlsx
@@ -214,43 +214,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -447,98 +447,98 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="Q2" s="0" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="Q2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4"/>
-      <c r="C3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5"/>
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="Q3" s="0" t="s">
+      <c r="G3" s="6"/>
+      <c r="Q3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <f aca="false">IF(COUNTIF($C$11:$C$13,"All")&gt;0,SUMIFS(Data!$C:$C,Data!$A:$A,$C$2),SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$11)+SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$12)+SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$13))</f>
+      <c r="C4" s="7" t="n">
+        <f aca="false">IF(COUNTIF($C$11:$C$13,"All")&gt;0,SUMIF(Data!$A:$A,$C$2,Data!$C:$C),SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$11)+SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$12)+SUMIFS(Data!$C:$C,Data!$A:$A,$C$2,Data!$B:$B,$C$13))</f>
         <v>92</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="Q4" s="0" t="s">
+      <c r="G4" s="6"/>
+      <c r="Q4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="Q5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="Q5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="G7" s="5"/>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="n">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -565,223 +565,223 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>88</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>72</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>71</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>69</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>84</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>4</v>
       </c>
     </row>
